--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 ELK BULL ALL HUNTS.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 ELK BULL ALL HUNTS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$O$354</definedName>
@@ -5498,7 +5498,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N74" s="3" t="inlineStr"/>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
           <t>3.7</t>
@@ -5567,7 +5571,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N75" s="5" t="inlineStr"/>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
       <c r="O75" s="5" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -5636,7 +5644,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N76" s="3" t="inlineStr"/>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -5705,7 +5717,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N77" s="5" t="inlineStr"/>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
       <c r="O77" s="5" t="inlineStr">
         <is>
           <t>50.0</t>
@@ -5774,7 +5790,11 @@
           <t>73.9</t>
         </is>
       </c>
-      <c r="N78" s="3" t="inlineStr"/>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
           <t>13.3</t>
@@ -5843,7 +5863,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="N79" s="5" t="inlineStr"/>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O79" s="5" t="inlineStr">
         <is>
           <t>11.0</t>
@@ -5912,7 +5936,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N80" s="3" t="inlineStr"/>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
           <t>10.4</t>
@@ -5981,7 +6009,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N81" s="5" t="inlineStr"/>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O81" s="5" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -6050,7 +6082,11 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="N82" s="3" t="inlineStr"/>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
           <t>12.3</t>
@@ -6119,7 +6155,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N83" s="5" t="inlineStr"/>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O83" s="5" t="inlineStr">
         <is>
           <t>10.5</t>
@@ -6188,7 +6228,11 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="N84" s="3" t="inlineStr"/>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
           <t>11.5</t>
@@ -6257,7 +6301,11 @@
           <t>69.2</t>
         </is>
       </c>
-      <c r="N85" s="5" t="inlineStr"/>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O85" s="5" t="inlineStr">
         <is>
           <t>19.8</t>
@@ -6326,7 +6374,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N86" s="3" t="inlineStr"/>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O86" s="3" t="inlineStr">
         <is>
           <t>14.0</t>
@@ -6395,7 +6447,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N87" s="5" t="inlineStr"/>
+      <c r="N87" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O87" s="5" t="inlineStr">
         <is>
           <t>8.3</t>
@@ -6464,7 +6520,11 @@
           <t>66.7</t>
         </is>
       </c>
-      <c r="N88" s="3" t="inlineStr"/>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
           <t>14.9</t>
@@ -8108,7 +8168,11 @@
           <t>80.0</t>
         </is>
       </c>
-      <c r="N112" s="3" t="inlineStr"/>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
           <t>14.0</t>
@@ -8177,7 +8241,11 @@
           <t>85.7</t>
         </is>
       </c>
-      <c r="N113" s="5" t="inlineStr"/>
+      <c r="N113" s="5" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
       <c r="O113" s="5" t="inlineStr">
         <is>
           <t>13.0</t>
@@ -15800,7 +15868,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N224" s="3" t="inlineStr"/>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O224" s="3" t="inlineStr">
         <is>
           <t>9.0</t>
@@ -15849,7 +15921,11 @@
       <c r="K225" s="4" t="inlineStr"/>
       <c r="L225" s="5" t="inlineStr"/>
       <c r="M225" s="5" t="inlineStr"/>
-      <c r="N225" s="5" t="inlineStr"/>
+      <c r="N225" s="5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
       <c r="O225" s="5" t="inlineStr"/>
     </row>
     <row r="226" ht="28" customHeight="1">
@@ -15894,7 +15970,11 @@
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="3" t="inlineStr"/>
       <c r="M226" s="3" t="inlineStr"/>
-      <c r="N226" s="3" t="inlineStr"/>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O226" s="3" t="inlineStr"/>
     </row>
     <row r="227" ht="28" customHeight="1">
@@ -15939,7 +16019,11 @@
       <c r="K227" s="4" t="inlineStr"/>
       <c r="L227" s="5" t="inlineStr"/>
       <c r="M227" s="5" t="inlineStr"/>
-      <c r="N227" s="5" t="inlineStr"/>
+      <c r="N227" s="5" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
       <c r="O227" s="5" t="inlineStr"/>
     </row>
     <row r="228" ht="28" customHeight="1">
@@ -15984,7 +16068,11 @@
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="3" t="inlineStr"/>
       <c r="M228" s="3" t="inlineStr"/>
-      <c r="N228" s="3" t="inlineStr"/>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O228" s="3" t="inlineStr"/>
     </row>
     <row r="229" ht="28" customHeight="1">
@@ -16029,7 +16117,11 @@
       <c r="K229" s="4" t="inlineStr"/>
       <c r="L229" s="5" t="inlineStr"/>
       <c r="M229" s="5" t="inlineStr"/>
-      <c r="N229" s="5" t="inlineStr"/>
+      <c r="N229" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O229" s="5" t="inlineStr"/>
     </row>
     <row r="230" ht="28" customHeight="1">
@@ -16074,7 +16166,11 @@
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="3" t="inlineStr"/>
       <c r="M230" s="3" t="inlineStr"/>
-      <c r="N230" s="3" t="inlineStr"/>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O230" s="3" t="inlineStr"/>
     </row>
     <row r="231" ht="28" customHeight="1">
@@ -16119,7 +16215,11 @@
       <c r="K231" s="4" t="inlineStr"/>
       <c r="L231" s="5" t="inlineStr"/>
       <c r="M231" s="5" t="inlineStr"/>
-      <c r="N231" s="5" t="inlineStr"/>
+      <c r="N231" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O231" s="5" t="inlineStr"/>
     </row>
     <row r="232" ht="28" customHeight="1">
@@ -16164,7 +16264,11 @@
       <c r="K232" s="2" t="inlineStr"/>
       <c r="L232" s="3" t="inlineStr"/>
       <c r="M232" s="3" t="inlineStr"/>
-      <c r="N232" s="3" t="inlineStr"/>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O232" s="3" t="inlineStr"/>
     </row>
     <row r="233" ht="28" customHeight="1">
@@ -16209,7 +16313,11 @@
       <c r="K233" s="4" t="inlineStr"/>
       <c r="L233" s="5" t="inlineStr"/>
       <c r="M233" s="5" t="inlineStr"/>
-      <c r="N233" s="5" t="inlineStr"/>
+      <c r="N233" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O233" s="5" t="inlineStr"/>
     </row>
     <row r="234" ht="28" customHeight="1">
@@ -16254,7 +16362,11 @@
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="3" t="inlineStr"/>
       <c r="M234" s="3" t="inlineStr"/>
-      <c r="N234" s="3" t="inlineStr"/>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O234" s="3" t="inlineStr"/>
     </row>
     <row r="235" ht="28" customHeight="1">
@@ -16299,7 +16411,11 @@
       <c r="K235" s="4" t="inlineStr"/>
       <c r="L235" s="5" t="inlineStr"/>
       <c r="M235" s="5" t="inlineStr"/>
-      <c r="N235" s="5" t="inlineStr"/>
+      <c r="N235" s="5" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O235" s="5" t="inlineStr"/>
     </row>
     <row r="236" ht="28" customHeight="1">
@@ -16344,7 +16460,11 @@
       <c r="K236" s="2" t="inlineStr"/>
       <c r="L236" s="3" t="inlineStr"/>
       <c r="M236" s="3" t="inlineStr"/>
-      <c r="N236" s="3" t="inlineStr"/>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O236" s="3" t="inlineStr"/>
     </row>
     <row r="237" ht="28" customHeight="1">
@@ -16389,7 +16509,11 @@
       <c r="K237" s="4" t="inlineStr"/>
       <c r="L237" s="5" t="inlineStr"/>
       <c r="M237" s="5" t="inlineStr"/>
-      <c r="N237" s="5" t="inlineStr"/>
+      <c r="N237" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O237" s="5" t="inlineStr"/>
     </row>
     <row r="238" ht="28" customHeight="1">
@@ -16442,7 +16566,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N238" s="3" t="inlineStr"/>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O238" s="3" t="inlineStr">
         <is>
           <t>20.0</t>
@@ -16499,7 +16627,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N239" s="5" t="inlineStr"/>
+      <c r="N239" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O239" s="5" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -16548,7 +16680,11 @@
       <c r="K240" s="2" t="inlineStr"/>
       <c r="L240" s="3" t="inlineStr"/>
       <c r="M240" s="3" t="inlineStr"/>
-      <c r="N240" s="3" t="inlineStr"/>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O240" s="3" t="inlineStr"/>
     </row>
     <row r="241" ht="28" customHeight="1">
@@ -16593,7 +16729,11 @@
       <c r="K241" s="4" t="inlineStr"/>
       <c r="L241" s="5" t="inlineStr"/>
       <c r="M241" s="5" t="inlineStr"/>
-      <c r="N241" s="5" t="inlineStr"/>
+      <c r="N241" s="5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
       <c r="O241" s="5" t="inlineStr"/>
     </row>
     <row r="242" ht="28" customHeight="1">
@@ -16638,7 +16778,11 @@
       <c r="K242" s="2" t="inlineStr"/>
       <c r="L242" s="3" t="inlineStr"/>
       <c r="M242" s="3" t="inlineStr"/>
-      <c r="N242" s="3" t="inlineStr"/>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O242" s="3" t="inlineStr"/>
     </row>
     <row r="243" ht="28" customHeight="1">
@@ -16683,7 +16827,11 @@
       <c r="K243" s="4" t="inlineStr"/>
       <c r="L243" s="5" t="inlineStr"/>
       <c r="M243" s="5" t="inlineStr"/>
-      <c r="N243" s="5" t="inlineStr"/>
+      <c r="N243" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O243" s="5" t="inlineStr"/>
     </row>
     <row r="244" ht="28" customHeight="1">
@@ -16736,7 +16884,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N244" s="3" t="inlineStr"/>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O244" s="3" t="inlineStr">
         <is>
           <t>3.0</t>
@@ -16785,7 +16937,11 @@
       <c r="K245" s="4" t="inlineStr"/>
       <c r="L245" s="5" t="inlineStr"/>
       <c r="M245" s="5" t="inlineStr"/>
-      <c r="N245" s="5" t="inlineStr"/>
+      <c r="N245" s="5" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
       <c r="O245" s="5" t="inlineStr"/>
     </row>
     <row r="246" ht="28" customHeight="1">
@@ -16830,7 +16986,11 @@
       <c r="K246" s="2" t="inlineStr"/>
       <c r="L246" s="3" t="inlineStr"/>
       <c r="M246" s="3" t="inlineStr"/>
-      <c r="N246" s="3" t="inlineStr"/>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
       <c r="O246" s="3" t="inlineStr"/>
     </row>
     <row r="247" ht="28" customHeight="1">
@@ -16883,7 +17043,11 @@
           <t>40.0</t>
         </is>
       </c>
-      <c r="N247" s="5" t="inlineStr"/>
+      <c r="N247" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O247" s="5" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -16940,7 +17104,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N248" s="3" t="inlineStr"/>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O248" s="3" t="inlineStr">
         <is>
           <t>5.0</t>
@@ -16989,7 +17157,11 @@
       <c r="K249" s="4" t="inlineStr"/>
       <c r="L249" s="5" t="inlineStr"/>
       <c r="M249" s="5" t="inlineStr"/>
-      <c r="N249" s="5" t="inlineStr"/>
+      <c r="N249" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O249" s="5" t="inlineStr"/>
     </row>
     <row r="250" ht="28" customHeight="1">
@@ -17034,7 +17206,11 @@
       <c r="K250" s="2" t="inlineStr"/>
       <c r="L250" s="3" t="inlineStr"/>
       <c r="M250" s="3" t="inlineStr"/>
-      <c r="N250" s="3" t="inlineStr"/>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O250" s="3" t="inlineStr"/>
     </row>
     <row r="251" ht="28" customHeight="1">
@@ -17079,7 +17255,11 @@
       <c r="K251" s="4" t="inlineStr"/>
       <c r="L251" s="5" t="inlineStr"/>
       <c r="M251" s="5" t="inlineStr"/>
-      <c r="N251" s="5" t="inlineStr"/>
+      <c r="N251" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O251" s="5" t="inlineStr"/>
     </row>
     <row r="252" ht="28" customHeight="1">
@@ -17124,7 +17304,11 @@
       <c r="K252" s="2" t="inlineStr"/>
       <c r="L252" s="3" t="inlineStr"/>
       <c r="M252" s="3" t="inlineStr"/>
-      <c r="N252" s="3" t="inlineStr"/>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O252" s="3" t="inlineStr"/>
     </row>
     <row r="253" ht="28" customHeight="1">
@@ -17169,7 +17353,11 @@
       <c r="K253" s="4" t="inlineStr"/>
       <c r="L253" s="5" t="inlineStr"/>
       <c r="M253" s="5" t="inlineStr"/>
-      <c r="N253" s="5" t="inlineStr"/>
+      <c r="N253" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O253" s="5" t="inlineStr"/>
     </row>
     <row r="254" ht="28" customHeight="1">
@@ -17214,7 +17402,11 @@
       <c r="K254" s="2" t="inlineStr"/>
       <c r="L254" s="3" t="inlineStr"/>
       <c r="M254" s="3" t="inlineStr"/>
-      <c r="N254" s="3" t="inlineStr"/>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O254" s="3" t="inlineStr"/>
     </row>
     <row r="255" ht="28" customHeight="1">
@@ -17267,7 +17459,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N255" s="5" t="inlineStr"/>
+      <c r="N255" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O255" s="5" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -17316,7 +17512,11 @@
       <c r="K256" s="2" t="inlineStr"/>
       <c r="L256" s="3" t="inlineStr"/>
       <c r="M256" s="3" t="inlineStr"/>
-      <c r="N256" s="3" t="inlineStr"/>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O256" s="3" t="inlineStr"/>
     </row>
     <row r="257" ht="28" customHeight="1">
@@ -17361,7 +17561,11 @@
       <c r="K257" s="4" t="inlineStr"/>
       <c r="L257" s="5" t="inlineStr"/>
       <c r="M257" s="5" t="inlineStr"/>
-      <c r="N257" s="5" t="inlineStr"/>
+      <c r="N257" s="5" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O257" s="5" t="inlineStr"/>
     </row>
     <row r="258" ht="28" customHeight="1">
@@ -17406,7 +17610,11 @@
       <c r="K258" s="2" t="inlineStr"/>
       <c r="L258" s="3" t="inlineStr"/>
       <c r="M258" s="3" t="inlineStr"/>
-      <c r="N258" s="3" t="inlineStr"/>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O258" s="3" t="inlineStr"/>
     </row>
     <row r="259" ht="28" customHeight="1">
@@ -17451,7 +17659,11 @@
       <c r="K259" s="4" t="inlineStr"/>
       <c r="L259" s="5" t="inlineStr"/>
       <c r="M259" s="5" t="inlineStr"/>
-      <c r="N259" s="5" t="inlineStr"/>
+      <c r="N259" s="5" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O259" s="5" t="inlineStr"/>
     </row>
     <row r="260" ht="28" customHeight="1">
@@ -17504,7 +17716,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N260" s="3" t="inlineStr"/>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O260" s="3" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -17553,7 +17769,11 @@
       <c r="K261" s="4" t="inlineStr"/>
       <c r="L261" s="5" t="inlineStr"/>
       <c r="M261" s="5" t="inlineStr"/>
-      <c r="N261" s="5" t="inlineStr"/>
+      <c r="N261" s="5" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O261" s="5" t="inlineStr"/>
     </row>
     <row r="262" ht="28" customHeight="1">
@@ -17598,7 +17818,11 @@
       <c r="K262" s="2" t="inlineStr"/>
       <c r="L262" s="3" t="inlineStr"/>
       <c r="M262" s="3" t="inlineStr"/>
-      <c r="N262" s="3" t="inlineStr"/>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O262" s="3" t="inlineStr"/>
     </row>
     <row r="263" ht="28" customHeight="1">
@@ -17651,7 +17875,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N263" s="5" t="inlineStr"/>
+      <c r="N263" s="5" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O263" s="5" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -17708,7 +17936,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N264" s="3" t="inlineStr"/>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O264" s="3" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -17757,7 +17989,11 @@
       <c r="K265" s="4" t="inlineStr"/>
       <c r="L265" s="5" t="inlineStr"/>
       <c r="M265" s="5" t="inlineStr"/>
-      <c r="N265" s="5" t="inlineStr"/>
+      <c r="N265" s="5" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O265" s="5" t="inlineStr"/>
     </row>
     <row r="266" ht="28" customHeight="1">
@@ -17810,7 +18046,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N266" s="3" t="inlineStr"/>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O266" s="3" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -17859,7 +18099,11 @@
       <c r="K267" s="4" t="inlineStr"/>
       <c r="L267" s="5" t="inlineStr"/>
       <c r="M267" s="5" t="inlineStr"/>
-      <c r="N267" s="5" t="inlineStr"/>
+      <c r="N267" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O267" s="5" t="inlineStr"/>
     </row>
     <row r="268" ht="28" customHeight="1">
@@ -17912,7 +18156,11 @@
           <t>57.1</t>
         </is>
       </c>
-      <c r="N268" s="3" t="inlineStr"/>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O268" s="3" t="inlineStr">
         <is>
           <t>3.5</t>
@@ -17961,7 +18209,11 @@
       <c r="K269" s="4" t="inlineStr"/>
       <c r="L269" s="5" t="inlineStr"/>
       <c r="M269" s="5" t="inlineStr"/>
-      <c r="N269" s="5" t="inlineStr"/>
+      <c r="N269" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O269" s="5" t="inlineStr"/>
     </row>
     <row r="270" ht="28" customHeight="1">
@@ -18006,7 +18258,11 @@
       <c r="K270" s="2" t="inlineStr"/>
       <c r="L270" s="3" t="inlineStr"/>
       <c r="M270" s="3" t="inlineStr"/>
-      <c r="N270" s="3" t="inlineStr"/>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O270" s="3" t="inlineStr"/>
     </row>
     <row r="271" ht="28" customHeight="1">
@@ -18051,7 +18307,11 @@
       <c r="K271" s="4" t="inlineStr"/>
       <c r="L271" s="5" t="inlineStr"/>
       <c r="M271" s="5" t="inlineStr"/>
-      <c r="N271" s="5" t="inlineStr"/>
+      <c r="N271" s="5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
       <c r="O271" s="5" t="inlineStr"/>
     </row>
     <row r="272" ht="28" customHeight="1">
@@ -18096,7 +18356,11 @@
       <c r="K272" s="2" t="inlineStr"/>
       <c r="L272" s="3" t="inlineStr"/>
       <c r="M272" s="3" t="inlineStr"/>
-      <c r="N272" s="3" t="inlineStr"/>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O272" s="3" t="inlineStr"/>
     </row>
     <row r="273" ht="28" customHeight="1">
@@ -18141,7 +18405,11 @@
       <c r="K273" s="4" t="inlineStr"/>
       <c r="L273" s="5" t="inlineStr"/>
       <c r="M273" s="5" t="inlineStr"/>
-      <c r="N273" s="5" t="inlineStr"/>
+      <c r="N273" s="5" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
       <c r="O273" s="5" t="inlineStr"/>
     </row>
     <row r="274" ht="28" customHeight="1">
@@ -18194,7 +18462,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="N274" s="3" t="inlineStr"/>
+      <c r="N274" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O274" s="3" t="inlineStr">
         <is>
           <t>4.5</t>
@@ -18243,7 +18515,11 @@
       <c r="K275" s="4" t="inlineStr"/>
       <c r="L275" s="5" t="inlineStr"/>
       <c r="M275" s="5" t="inlineStr"/>
-      <c r="N275" s="5" t="inlineStr"/>
+      <c r="N275" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O275" s="5" t="inlineStr"/>
     </row>
     <row r="276" ht="28" customHeight="1">
@@ -18288,7 +18564,11 @@
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="3" t="inlineStr"/>
       <c r="M276" s="3" t="inlineStr"/>
-      <c r="N276" s="3" t="inlineStr"/>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O276" s="3" t="inlineStr"/>
     </row>
     <row r="277" ht="28" customHeight="1">
@@ -18333,7 +18613,11 @@
       <c r="K277" s="4" t="inlineStr"/>
       <c r="L277" s="5" t="inlineStr"/>
       <c r="M277" s="5" t="inlineStr"/>
-      <c r="N277" s="5" t="inlineStr"/>
+      <c r="N277" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O277" s="5" t="inlineStr"/>
     </row>
     <row r="278" ht="28" customHeight="1">
@@ -18378,7 +18662,11 @@
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="3" t="inlineStr"/>
       <c r="M278" s="3" t="inlineStr"/>
-      <c r="N278" s="3" t="inlineStr"/>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O278" s="3" t="inlineStr"/>
     </row>
     <row r="279" ht="28" customHeight="1">
@@ -18423,7 +18711,11 @@
       <c r="K279" s="4" t="inlineStr"/>
       <c r="L279" s="5" t="inlineStr"/>
       <c r="M279" s="5" t="inlineStr"/>
-      <c r="N279" s="5" t="inlineStr"/>
+      <c r="N279" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O279" s="5" t="inlineStr"/>
     </row>
     <row r="280" ht="28" customHeight="1">
@@ -18468,7 +18760,11 @@
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="3" t="inlineStr"/>
       <c r="M280" s="3" t="inlineStr"/>
-      <c r="N280" s="3" t="inlineStr"/>
+      <c r="N280" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O280" s="3" t="inlineStr"/>
     </row>
     <row r="281" ht="28" customHeight="1">
@@ -18513,7 +18809,11 @@
       <c r="K281" s="4" t="inlineStr"/>
       <c r="L281" s="5" t="inlineStr"/>
       <c r="M281" s="5" t="inlineStr"/>
-      <c r="N281" s="5" t="inlineStr"/>
+      <c r="N281" s="5" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O281" s="5" t="inlineStr"/>
     </row>
     <row r="282" ht="28" customHeight="1">
@@ -18558,7 +18858,11 @@
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
-      <c r="N282" s="3" t="inlineStr"/>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O282" s="3" t="inlineStr"/>
     </row>
     <row r="283" ht="28" customHeight="1">
@@ -18603,7 +18907,11 @@
       <c r="K283" s="4" t="inlineStr"/>
       <c r="L283" s="5" t="inlineStr"/>
       <c r="M283" s="5" t="inlineStr"/>
-      <c r="N283" s="5" t="inlineStr"/>
+      <c r="N283" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O283" s="5" t="inlineStr"/>
     </row>
     <row r="284" ht="28" customHeight="1">
@@ -18656,7 +18964,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N284" s="3" t="inlineStr"/>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O284" s="3" t="inlineStr">
         <is>
           <t>7.0</t>
@@ -18713,7 +19025,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N285" s="5" t="inlineStr"/>
+      <c r="N285" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O285" s="5" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -18770,7 +19086,11 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="N286" s="3" t="inlineStr"/>
+      <c r="N286" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O286" s="3" t="inlineStr">
         <is>
           <t>2.7</t>
@@ -18819,7 +19139,11 @@
       <c r="K287" s="4" t="inlineStr"/>
       <c r="L287" s="5" t="inlineStr"/>
       <c r="M287" s="5" t="inlineStr"/>
-      <c r="N287" s="5" t="inlineStr"/>
+      <c r="N287" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O287" s="5" t="inlineStr"/>
     </row>
     <row r="288" ht="28" customHeight="1">
@@ -18999,7 +19323,11 @@
       <c r="K291" s="4" t="inlineStr"/>
       <c r="L291" s="5" t="inlineStr"/>
       <c r="M291" s="5" t="inlineStr"/>
-      <c r="N291" s="5" t="inlineStr"/>
+      <c r="N291" s="5" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
       <c r="O291" s="5" t="inlineStr"/>
     </row>
     <row r="292" ht="28" customHeight="1">
@@ -19187,7 +19515,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N295" s="5" t="inlineStr"/>
+      <c r="N295" s="5" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
       <c r="O295" s="5" t="inlineStr">
         <is>
           <t>6.0</t>
@@ -19236,7 +19568,11 @@
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="3" t="inlineStr"/>
       <c r="M296" s="3" t="inlineStr"/>
-      <c r="N296" s="3" t="inlineStr"/>
+      <c r="N296" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O296" s="3" t="inlineStr"/>
     </row>
     <row r="297" ht="28" customHeight="1">
@@ -19281,7 +19617,11 @@
       <c r="K297" s="4" t="inlineStr"/>
       <c r="L297" s="5" t="inlineStr"/>
       <c r="M297" s="5" t="inlineStr"/>
-      <c r="N297" s="5" t="inlineStr"/>
+      <c r="N297" s="5" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
       <c r="O297" s="5" t="inlineStr"/>
     </row>
     <row r="298" ht="28" customHeight="1">
@@ -19326,7 +19666,11 @@
       <c r="K298" s="2" t="inlineStr"/>
       <c r="L298" s="3" t="inlineStr"/>
       <c r="M298" s="3" t="inlineStr"/>
-      <c r="N298" s="3" t="inlineStr"/>
+      <c r="N298" s="3" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
       <c r="O298" s="3" t="inlineStr"/>
     </row>
     <row r="299" ht="28" customHeight="1">
@@ -19424,7 +19768,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N300" s="3" t="inlineStr"/>
+      <c r="N300" s="3" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
       <c r="O300" s="3" t="inlineStr">
         <is>
           <t>3.0</t>
@@ -19473,7 +19821,11 @@
       <c r="K301" s="4" t="inlineStr"/>
       <c r="L301" s="5" t="inlineStr"/>
       <c r="M301" s="5" t="inlineStr"/>
-      <c r="N301" s="5" t="inlineStr"/>
+      <c r="N301" s="5" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
       <c r="O301" s="5" t="inlineStr"/>
     </row>
     <row r="302" ht="28" customHeight="1">
@@ -19567,7 +19919,11 @@
         </is>
       </c>
       <c r="M303" s="5" t="inlineStr"/>
-      <c r="N303" s="5" t="inlineStr"/>
+      <c r="N303" s="5" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
       <c r="O303" s="5" t="inlineStr"/>
     </row>
     <row r="304" ht="28" customHeight="1">
@@ -19612,7 +19968,11 @@
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="3" t="inlineStr"/>
       <c r="M304" s="3" t="inlineStr"/>
-      <c r="N304" s="3" t="inlineStr"/>
+      <c r="N304" s="3" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
       <c r="O304" s="3" t="inlineStr"/>
     </row>
     <row r="305" ht="28" customHeight="1">
@@ -19657,7 +20017,11 @@
       <c r="K305" s="4" t="inlineStr"/>
       <c r="L305" s="5" t="inlineStr"/>
       <c r="M305" s="5" t="inlineStr"/>
-      <c r="N305" s="5" t="inlineStr"/>
+      <c r="N305" s="5" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O305" s="5" t="inlineStr"/>
     </row>
     <row r="306" ht="28" customHeight="1">
@@ -19702,7 +20066,11 @@
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="3" t="inlineStr"/>
       <c r="M306" s="3" t="inlineStr"/>
-      <c r="N306" s="3" t="inlineStr"/>
+      <c r="N306" s="3" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
       <c r="O306" s="3" t="inlineStr"/>
     </row>
     <row r="307" ht="28" customHeight="1">
@@ -19747,7 +20115,11 @@
       <c r="K307" s="4" t="inlineStr"/>
       <c r="L307" s="5" t="inlineStr"/>
       <c r="M307" s="5" t="inlineStr"/>
-      <c r="N307" s="5" t="inlineStr"/>
+      <c r="N307" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O307" s="5" t="inlineStr"/>
     </row>
     <row r="308" ht="28" customHeight="1">
@@ -19792,7 +20164,11 @@
       <c r="K308" s="2" t="inlineStr"/>
       <c r="L308" s="3" t="inlineStr"/>
       <c r="M308" s="3" t="inlineStr"/>
-      <c r="N308" s="3" t="inlineStr"/>
+      <c r="N308" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O308" s="3" t="inlineStr"/>
     </row>
     <row r="309" ht="28" customHeight="1">
@@ -20683,7 +21059,11 @@
       <c r="K327" s="4" t="inlineStr"/>
       <c r="L327" s="5" t="inlineStr"/>
       <c r="M327" s="5" t="inlineStr"/>
-      <c r="N327" s="5" t="inlineStr"/>
+      <c r="N327" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O327" s="5" t="inlineStr"/>
     </row>
     <row r="328" ht="28" customHeight="1">
@@ -20736,7 +21116,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N328" s="3" t="inlineStr"/>
+      <c r="N328" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O328" s="3" t="inlineStr">
         <is>
           <t>9.0</t>
@@ -20785,7 +21169,11 @@
       <c r="K329" s="4" t="inlineStr"/>
       <c r="L329" s="5" t="inlineStr"/>
       <c r="M329" s="5" t="inlineStr"/>
-      <c r="N329" s="5" t="inlineStr"/>
+      <c r="N329" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O329" s="5" t="inlineStr"/>
     </row>
     <row r="330" ht="28" customHeight="1">
@@ -20838,7 +21226,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N330" s="3" t="inlineStr"/>
+      <c r="N330" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O330" s="3" t="inlineStr">
         <is>
           <t>9.0</t>
@@ -20887,7 +21279,11 @@
       <c r="K331" s="4" t="inlineStr"/>
       <c r="L331" s="5" t="inlineStr"/>
       <c r="M331" s="5" t="inlineStr"/>
-      <c r="N331" s="5" t="inlineStr"/>
+      <c r="N331" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O331" s="5" t="inlineStr"/>
     </row>
     <row r="332" ht="28" customHeight="1">
@@ -20932,7 +21328,11 @@
       <c r="K332" s="2" t="inlineStr"/>
       <c r="L332" s="3" t="inlineStr"/>
       <c r="M332" s="3" t="inlineStr"/>
-      <c r="N332" s="3" t="inlineStr"/>
+      <c r="N332" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O332" s="3" t="inlineStr"/>
     </row>
     <row r="333" ht="28" customHeight="1">
@@ -20977,7 +21377,11 @@
       <c r="K333" s="4" t="inlineStr"/>
       <c r="L333" s="5" t="inlineStr"/>
       <c r="M333" s="5" t="inlineStr"/>
-      <c r="N333" s="5" t="inlineStr"/>
+      <c r="N333" s="5" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O333" s="5" t="inlineStr"/>
     </row>
     <row r="334" ht="28" customHeight="1">
@@ -21022,7 +21426,11 @@
       <c r="K334" s="2" t="inlineStr"/>
       <c r="L334" s="3" t="inlineStr"/>
       <c r="M334" s="3" t="inlineStr"/>
-      <c r="N334" s="3" t="inlineStr"/>
+      <c r="N334" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O334" s="3" t="inlineStr"/>
     </row>
     <row r="335" ht="28" customHeight="1">
@@ -21067,7 +21475,11 @@
       <c r="K335" s="4" t="inlineStr"/>
       <c r="L335" s="5" t="inlineStr"/>
       <c r="M335" s="5" t="inlineStr"/>
-      <c r="N335" s="5" t="inlineStr"/>
+      <c r="N335" s="5" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O335" s="5" t="inlineStr"/>
     </row>
     <row r="336" ht="28" customHeight="1">
@@ -21112,7 +21524,11 @@
       <c r="K336" s="2" t="inlineStr"/>
       <c r="L336" s="3" t="inlineStr"/>
       <c r="M336" s="3" t="inlineStr"/>
-      <c r="N336" s="3" t="inlineStr"/>
+      <c r="N336" s="3" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
       <c r="O336" s="3" t="inlineStr"/>
     </row>
     <row r="337" ht="28" customHeight="1">
@@ -21292,7 +21708,11 @@
       <c r="K340" s="2" t="inlineStr"/>
       <c r="L340" s="3" t="inlineStr"/>
       <c r="M340" s="3" t="inlineStr"/>
-      <c r="N340" s="3" t="inlineStr"/>
+      <c r="N340" s="3" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O340" s="3" t="inlineStr"/>
     </row>
     <row r="341" ht="28" customHeight="1">
@@ -21345,7 +21765,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N341" s="5" t="inlineStr"/>
+      <c r="N341" s="5" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O341" s="5" t="inlineStr">
         <is>
           <t>11.0</t>
@@ -21394,7 +21818,11 @@
       <c r="K342" s="2" t="inlineStr"/>
       <c r="L342" s="3" t="inlineStr"/>
       <c r="M342" s="3" t="inlineStr"/>
-      <c r="N342" s="3" t="inlineStr"/>
+      <c r="N342" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O342" s="3" t="inlineStr"/>
     </row>
     <row r="343" ht="28" customHeight="1">
@@ -21447,7 +21875,11 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="N343" s="5" t="inlineStr"/>
+      <c r="N343" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O343" s="5" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -21598,7 +22030,11 @@
       <c r="K346" s="2" t="inlineStr"/>
       <c r="L346" s="3" t="inlineStr"/>
       <c r="M346" s="3" t="inlineStr"/>
-      <c r="N346" s="3" t="inlineStr"/>
+      <c r="N346" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O346" s="3" t="inlineStr"/>
     </row>
     <row r="347" ht="28" customHeight="1">
